--- a/라만_벤치마크.xlsx
+++ b/라만_벤치마크.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\gemma_raman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB2984D8-B3FA-457A-8B69-042797635F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ADA25A4-AA81-4D0D-B3A7-EE006D6CD2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="8085" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task_채점기준" sheetId="1" r:id="rId1"/>

--- a/라만_벤치마크.xlsx
+++ b/라만_벤치마크.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\gemma_raman\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seoja\OneDrive\Desktop\gemma4_raman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ADA25A4-AA81-4D0D-B3A7-EE006D6CD2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E70A94AA-3F67-439B-87C5-7CDC7004954F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16110" yWindow="-110" windowWidth="16220" windowHeight="25100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task_채점기준" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="492">
   <si>
     <t>Task</t>
   </si>
@@ -1092,18 +1092,6 @@
   </si>
   <si>
     <t>Load the input polystyrene Raman spectrum and display it as a line graph of Raman shift versus intensity.</t>
-  </si>
-  <si>
-    <t>Presetup: Fix the camera image and pixel-to-stage coordinate transform and prepare the centers of the 4 regions to be detected. / Required files/data: One camera image containing 2x2 regions of interest. / Mockup condition: None. Directly executable on a real Raman instrument.</t>
-  </si>
-  <si>
-    <t>Passes if the four detected centers match the evaluation reference centers within 2 pixels each, each center is converted to coordinates and visited/measured once without duplication, and the total number of measurements is 4.</t>
-  </si>
-  <si>
-    <t>Assuming the centers of four measurement regions arbitrarily arranged in a 2x2 layout in the input camera image, move to the stage position corresponding to each center and measure a spectrum once each.</t>
-  </si>
-  <si>
-    <t>Vision+acquisition</t>
   </si>
   <si>
     <t>2. Sequence &amp; acquisition</t>
@@ -1549,7 +1537,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1591,7 +1579,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1601,12 +1589,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7A263A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1746,7 +1728,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1805,33 +1787,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1853,7 +1819,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9372E78-0839-4532-AB71-1F427108F364}" name="RamanBenchmarkTable3" displayName="RamanBenchmarkTable3" ref="A1:F129">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9372E78-0839-4532-AB71-1F427108F364}" name="RamanBenchmarkTable3" displayName="RamanBenchmarkTable3" ref="A1:F128">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="카테고리"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="복잡도"/>
@@ -2015,758 +1981,758 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F130"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:F129"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
     <col min="4" max="4" width="54" customWidth="1"/>
     <col min="5" max="5" width="88" customWidth="1"/>
     <col min="6" max="6" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.45" customHeight="1">
+    <row r="1" spans="1:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="21" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="21" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>458</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="26" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A2" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B2" s="23" t="s">
+      <c r="D3" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="21" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="D2" s="25" t="s">
+      <c r="C4" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>463</v>
       </c>
-      <c r="E2" s="25" t="s">
-        <v>455</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="26" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A3" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B3" s="23" t="s">
+      <c r="E6" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>462</v>
-      </c>
-      <c r="D3" s="27" t="s">
+      <c r="C7" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>464</v>
       </c>
-      <c r="E3" s="25" t="s">
-        <v>453</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="26" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A4" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B4" s="23" t="s">
+      <c r="E7" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="D4" s="25" t="s">
+      <c r="C8" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="E4" s="25" t="s">
-        <v>451</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B5" s="23" t="s">
+      <c r="E9" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>466</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>449</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A6" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="23" t="s">
+      <c r="C10" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>467</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>447</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A7" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="C11" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>445</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A8" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>470</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A9" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>441</v>
-      </c>
-      <c r="D9" s="27" t="s">
+      <c r="C12" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>469</v>
       </c>
-      <c r="E9" s="27" t="s">
-        <v>440</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A10" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>471</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>438</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A11" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>413</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>472</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>436</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A12" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>473</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>434</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="26.1" customHeight="1">
+      <c r="E12" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>423</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="21" customFormat="1" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="D17" s="23" t="s">
         <v>474</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A14" s="22" t="s">
+      <c r="E17" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="B14" s="23" t="s">
+    </row>
+    <row r="19" spans="1:6" s="21" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>475</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A15" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="D15" s="27" t="s">
+      <c r="C19" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="E15" s="27" t="s">
-        <v>427</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A16" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>477</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="26" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A17" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>478</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A18" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>479</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>419</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="26" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A19" s="22" t="s">
-        <v>414</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>480</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>416</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="32.1" customHeight="1">
+      <c r="E19" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D20" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="E23" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>483</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="39" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="39" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="39" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="39" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="39" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="39" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A35" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A36" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>365</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" s="21" customFormat="1" ht="48" customHeight="1">
-      <c r="A37" s="17" t="s">
-        <v>361</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>359</v>
-      </c>
-      <c r="E37" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="F37" s="18" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="26.1" customHeight="1">
+    </row>
+    <row r="37" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>289</v>
       </c>
@@ -2774,19 +2740,19 @@
         <v>1</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="39" customHeight="1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>289</v>
       </c>
@@ -2797,16 +2763,16 @@
         <v>293</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="39" customHeight="1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>289</v>
       </c>
@@ -2817,16 +2783,16 @@
         <v>293</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="39" customHeight="1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>289</v>
       </c>
@@ -2837,16 +2803,16 @@
         <v>293</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="26.1" customHeight="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>289</v>
       </c>
@@ -2854,19 +2820,19 @@
         <v>1</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>293</v>
+        <v>341</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="39" customHeight="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>289</v>
       </c>
@@ -2874,39 +2840,39 @@
         <v>1</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="26.1" customHeight="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>289</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>300</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="39" customHeight="1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>289</v>
       </c>
@@ -2914,19 +2880,19 @@
         <v>2</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="39" customHeight="1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>289</v>
       </c>
@@ -2934,39 +2900,39 @@
         <v>2</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="39" customHeight="1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>289</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="26.1" customHeight="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>289</v>
       </c>
@@ -2974,39 +2940,39 @@
         <v>1</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="26.1" customHeight="1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>289</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="39" customHeight="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>289</v>
       </c>
@@ -3014,19 +2980,19 @@
         <v>2</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="26.1" customHeight="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>289</v>
       </c>
@@ -3034,19 +3000,19 @@
         <v>2</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="39" customHeight="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>289</v>
       </c>
@@ -3054,39 +3020,39 @@
         <v>2</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="39" customHeight="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>289</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>300</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="39" customHeight="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>289</v>
       </c>
@@ -3094,19 +3060,19 @@
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="26.1" customHeight="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>289</v>
       </c>
@@ -3117,56 +3083,56 @@
         <v>293</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="26.1" customHeight="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>289</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="39" customHeight="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="39" customHeight="1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>208</v>
       </c>
@@ -3174,19 +3140,19 @@
         <v>2</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="26.1" customHeight="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>208</v>
       </c>
@@ -3194,19 +3160,19 @@
         <v>2</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="39" customHeight="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>208</v>
       </c>
@@ -3214,19 +3180,19 @@
         <v>2</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="39" customHeight="1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>208</v>
       </c>
@@ -3234,19 +3200,19 @@
         <v>2</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="39" customHeight="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>208</v>
       </c>
@@ -3254,19 +3220,19 @@
         <v>2</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="39" customHeight="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>208</v>
       </c>
@@ -3274,19 +3240,19 @@
         <v>2</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="51.95" customHeight="1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>208</v>
       </c>
@@ -3294,19 +3260,19 @@
         <v>2</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="39" customHeight="1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>208</v>
       </c>
@@ -3314,19 +3280,19 @@
         <v>2</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="39" customHeight="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>208</v>
       </c>
@@ -3334,19 +3300,19 @@
         <v>2</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="39" customHeight="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>208</v>
       </c>
@@ -3354,19 +3320,19 @@
         <v>2</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="26.1" customHeight="1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>208</v>
       </c>
@@ -3374,19 +3340,19 @@
         <v>2</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="39" customHeight="1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>208</v>
       </c>
@@ -3394,19 +3360,19 @@
         <v>2</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="39" customHeight="1">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>208</v>
       </c>
@@ -3414,19 +3380,19 @@
         <v>2</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="39" customHeight="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>208</v>
       </c>
@@ -3434,19 +3400,19 @@
         <v>2</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="39" customHeight="1">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>208</v>
       </c>
@@ -3454,19 +3420,19 @@
         <v>2</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="26.1" customHeight="1">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>208</v>
       </c>
@@ -3474,19 +3440,19 @@
         <v>2</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="39" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>208</v>
       </c>
@@ -3494,19 +3460,19 @@
         <v>2</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="39" customHeight="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>208</v>
       </c>
@@ -3514,19 +3480,19 @@
         <v>2</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="39" customHeight="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>208</v>
       </c>
@@ -3534,39 +3500,39 @@
         <v>2</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="51.95" customHeight="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="26.1" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>133</v>
       </c>
@@ -3574,19 +3540,19 @@
         <v>2</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="39" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>133</v>
       </c>
@@ -3594,19 +3560,19 @@
         <v>2</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="39" customHeight="1">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>133</v>
       </c>
@@ -3614,19 +3580,19 @@
         <v>2</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="26.1" customHeight="1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>133</v>
       </c>
@@ -3634,19 +3600,19 @@
         <v>2</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="26.1" customHeight="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>133</v>
       </c>
@@ -3654,19 +3620,19 @@
         <v>2</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="26.1" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>133</v>
       </c>
@@ -3674,19 +3640,19 @@
         <v>2</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="26.1" customHeight="1">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>133</v>
       </c>
@@ -3694,19 +3660,19 @@
         <v>2</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="26.1" customHeight="1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>133</v>
       </c>
@@ -3714,19 +3680,19 @@
         <v>2</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>171</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="26.1" customHeight="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>133</v>
       </c>
@@ -3734,19 +3700,19 @@
         <v>2</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>171</v>
+        <v>168</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="26.1" customHeight="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>133</v>
       </c>
@@ -3754,19 +3720,19 @@
         <v>2</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="39" customHeight="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>133</v>
       </c>
@@ -3774,19 +3740,19 @@
         <v>2</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="26.1" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>133</v>
       </c>
@@ -3794,40 +3760,38 @@
         <v>2</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="39" customHeight="1">
-      <c r="A90" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="26.1" customHeight="1"/>
-    <row r="92" spans="1:6" ht="26.1" customHeight="1">
+      <c r="B91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>133</v>
       </c>
@@ -3835,17 +3799,19 @@
         <v>2</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="E92" s="1"/>
+        <v>149</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F92" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="39" customHeight="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>133</v>
       </c>
@@ -3853,19 +3819,19 @@
         <v>2</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="26.1" customHeight="1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>133</v>
       </c>
@@ -3873,19 +3839,19 @@
         <v>2</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="39" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>133</v>
       </c>
@@ -3893,19 +3859,19 @@
         <v>2</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="26.1" customHeight="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>133</v>
       </c>
@@ -3913,39 +3879,39 @@
         <v>2</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="26.1" customHeight="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="39" customHeight="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>80</v>
       </c>
@@ -3953,19 +3919,19 @@
         <v>2</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="39" customHeight="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>80</v>
       </c>
@@ -3976,16 +3942,16 @@
         <v>79</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="39" customHeight="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>80</v>
       </c>
@@ -3996,16 +3962,16 @@
         <v>79</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="39" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>80</v>
       </c>
@@ -4016,16 +3982,16 @@
         <v>79</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="39" customHeight="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>80</v>
       </c>
@@ -4033,19 +3999,19 @@
         <v>2</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="48" customHeight="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>80</v>
       </c>
@@ -4053,59 +4019,59 @@
         <v>2</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E103" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="39" customHeight="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="39" customHeight="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="39" customHeight="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>80</v>
       </c>
@@ -4113,19 +4079,19 @@
         <v>2</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="39" customHeight="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>80</v>
       </c>
@@ -4136,16 +4102,16 @@
         <v>79</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="39" customHeight="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>80</v>
       </c>
@@ -4153,19 +4119,19 @@
         <v>2</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="39" customHeight="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>80</v>
       </c>
@@ -4173,19 +4139,19 @@
         <v>2</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="39" customHeight="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>80</v>
       </c>
@@ -4193,19 +4159,19 @@
         <v>2</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="39" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>80</v>
       </c>
@@ -4216,36 +4182,36 @@
         <v>79</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="51.95" customHeight="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="39" customHeight="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>7</v>
       </c>
@@ -4253,19 +4219,19 @@
         <v>2</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="39" customHeight="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>7</v>
       </c>
@@ -4273,19 +4239,19 @@
         <v>2</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="51.95" customHeight="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>7</v>
       </c>
@@ -4293,19 +4259,19 @@
         <v>2</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="51.95" customHeight="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -4313,19 +4279,19 @@
         <v>2</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="51.95" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>7</v>
       </c>
@@ -4333,19 +4299,19 @@
         <v>2</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="51.95" customHeight="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>7</v>
       </c>
@@ -4353,19 +4319,19 @@
         <v>2</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="51.95" customHeight="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>7</v>
       </c>
@@ -4373,19 +4339,19 @@
         <v>2</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="51.95" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>7</v>
       </c>
@@ -4393,19 +4359,19 @@
         <v>2</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="51.95" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>7</v>
       </c>
@@ -4413,19 +4379,19 @@
         <v>2</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="39" customHeight="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>7</v>
       </c>
@@ -4433,19 +4399,19 @@
         <v>2</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="51.95" customHeight="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>7</v>
       </c>
@@ -4453,19 +4419,19 @@
         <v>2</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="51.95" customHeight="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -4473,19 +4439,19 @@
         <v>2</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="39" customHeight="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>7</v>
       </c>
@@ -4493,19 +4459,19 @@
         <v>2</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="51.95" customHeight="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>7</v>
       </c>
@@ -4513,19 +4479,19 @@
         <v>2</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="51.95" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>7</v>
       </c>
@@ -4533,19 +4499,19 @@
         <v>2</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="51.95" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>7</v>
       </c>
@@ -4553,55 +4519,35 @@
         <v>2</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="51.95" customHeight="1">
-      <c r="A129" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="51.95" customHeight="1">
-      <c r="A130" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C130" s="7" t="s">
+      <c r="B129" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D129" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E130" s="12" t="s">
+      <c r="E129" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="F129" s="5" t="s">
         <v>3</v>
       </c>
     </row>
